--- a/data/nzd0593/nzd0593.xlsx
+++ b/data/nzd0593/nzd0593.xlsx
@@ -29123,9 +29123,15 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+      <c r="F2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.0294</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.0622</v>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
@@ -29173,9 +29179,15 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
+      <c r="F3" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.0236</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.0476</v>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
@@ -29223,9 +29235,15 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
+      <c r="F4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.0129</v>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
@@ -29273,9 +29291,15 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
+      <c r="F5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.09520000000000001</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
@@ -29323,9 +29347,15 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+      <c r="F6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.1122</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -29373,9 +29403,15 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
+      <c r="F7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.1169</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -29423,9 +29459,15 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
+      <c r="F8" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.0187</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.0318</v>
+      </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -29473,9 +29515,15 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
+      <c r="F9" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.0187</v>
+      </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
@@ -29523,9 +29571,15 @@
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
+      <c r="F10" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.0133</v>
+      </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
@@ -29573,9 +29627,15 @@
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
+      <c r="F11" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.0111</v>
+      </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
@@ -29623,9 +29683,15 @@
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
+      <c r="F12" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.0165</v>
+      </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
@@ -29673,9 +29739,15 @@
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
+      <c r="F13" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.0111</v>
+      </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
@@ -29723,9 +29795,15 @@
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
+      <c r="F14" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.0116</v>
+      </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
@@ -29773,9 +29851,15 @@
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
+      <c r="F15" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.0121</v>
+      </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
@@ -29823,9 +29907,15 @@
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
+      <c r="F16" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.0237</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.056</v>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
@@ -29873,9 +29963,15 @@
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
+      <c r="F17" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.0786</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.1892</v>
+      </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
@@ -29923,9 +30019,15 @@
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
+      <c r="F18" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.0791</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.1532</v>
+      </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
@@ -29973,9 +30075,15 @@
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
+      <c r="F19" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.059</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.0805</v>
+      </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
@@ -30023,9 +30131,15 @@
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
+      <c r="F20" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.0449</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.06469999999999999</v>
+      </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
@@ -30073,9 +30187,15 @@
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
+      <c r="F21" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.0347</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.0504</v>
+      </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
@@ -30123,9 +30243,15 @@
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
+      <c r="F22" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.0497</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.0701</v>
+      </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
@@ -30173,9 +30299,15 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
+      <c r="F23" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.0587</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.0902</v>
+      </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
@@ -30223,9 +30355,15 @@
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
+      <c r="F24" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.09039999999999999</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.1699</v>
+      </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
@@ -30273,9 +30411,15 @@
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
+      <c r="F25" t="n">
+        <v>0.185</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.149</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
@@ -30323,9 +30467,15 @@
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
+      <c r="F26" t="n">
+        <v>0.115</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.0949</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.1534</v>
+      </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
@@ -30373,9 +30523,15 @@
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
+      <c r="F27" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.06660000000000001</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.1322</v>
+      </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
@@ -30423,9 +30579,15 @@
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
+      <c r="F28" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.0179</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.0267</v>
+      </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
@@ -30473,9 +30635,15 @@
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
+      <c r="F29" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.0147</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.0241</v>
+      </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
@@ -30523,9 +30691,15 @@
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
+      <c r="F30" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.0169</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.0274</v>
+      </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
@@ -30573,9 +30747,15 @@
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
+      <c r="F31" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.0243</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.0504</v>
+      </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
@@ -30623,9 +30803,15 @@
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
+      <c r="F32" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.0467</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.1182</v>
+      </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
@@ -30673,9 +30859,15 @@
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
+      <c r="F33" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.0684</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.133</v>
+      </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
@@ -30723,9 +30915,15 @@
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
+      <c r="F34" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.07049999999999999</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.115</v>
+      </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
@@ -30773,9 +30971,15 @@
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
+      <c r="F35" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.0696</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.114</v>
+      </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
@@ -30823,9 +31027,15 @@
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
+      <c r="F36" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.0373</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.0612</v>
+      </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
